--- a/history_matching/example/iter2/Cuts/RadiusShouldBe15/history_matching_config.xlsx
+++ b/history_matching/example/iter2/Cuts/RadiusShouldBe15/history_matching_config.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
   <si>
     <t>Parameter</t>
   </si>
@@ -67,166 +68,172 @@
     <t>Train</t>
   </si>
   <si>
-    <t>Data_20170712_104006.000000</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000001</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000002</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000003</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000004</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000005</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000006</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000007</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000008</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000009</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000010</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000011</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000012</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000013</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000014</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000015</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000016</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000017</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000018</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000019</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000020</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000021</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000022</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000023</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000024</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000025</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000026</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000027</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000028</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000029</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000030</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000031</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000032</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000033</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000034</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000035</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000036</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000037</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000038</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000039</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000040</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000041</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000042</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000043</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000044</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000045</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000046</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000047</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000048</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000049</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000050</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000051</t>
-  </si>
-  <si>
-    <t>Data_20170712_104006.000052</t>
+    <t>Data_20180119_074635.000000</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000001</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000002</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000003</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000004</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000005</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000006</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000007</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000008</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000009</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000010</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000011</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000012</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000013</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000014</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000015</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000016</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000017</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000018</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000019</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000020</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000021</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000022</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000023</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000024</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000025</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000026</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000027</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000028</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000029</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000030</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000031</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000032</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000033</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000034</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000035</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000036</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000037</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000038</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000039</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000040</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000041</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000042</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000043</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000044</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000045</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000046</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000047</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000048</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000049</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000050</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000051</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000052</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000053</t>
+  </si>
+  <si>
+    <t>Data_20180119_074635.000054</t>
   </si>
   <si>
     <t>Sim_Id</t>
@@ -668,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -699,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-5.405137365595422</v>
+        <v>-12.14684535151868</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.8830846696643</v>
+        <v>-19.8468228003866</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -719,10 +726,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>-10.40425993869515</v>
+        <v>4.904898148493372</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.476311445201773</v>
+        <v>1.967001998453881</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -739,10 +746,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>-20.7857936424723</v>
+        <v>10.17802948191527</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.232261528089538</v>
+        <v>-6.083306211143764</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -759,10 +766,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>6.227042732383623</v>
+        <v>-6.753743942882013</v>
       </c>
       <c r="D5" t="n">
-        <v>5.846666045038035</v>
+        <v>-22.76013445207743</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -779,10 +786,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-13.20516413704294</v>
+        <v>-5.189547005439286</v>
       </c>
       <c r="D6" t="n">
-        <v>1.261663540521198</v>
+        <v>-15.99828556386437</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -799,10 +806,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.148377553764135</v>
+        <v>-1.256059070692373</v>
       </c>
       <c r="D7" t="n">
-        <v>16.56232694657282</v>
+        <v>-18.05910606199234</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -819,10 +826,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.08906562902339488</v>
+        <v>-13.54903056732685</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.5373498725817</v>
+        <v>-17.39727569829309</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -839,10 +846,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.70434314501162</v>
+        <v>13.89487980954055</v>
       </c>
       <c r="D9" t="n">
-        <v>7.343673720746779</v>
+        <v>-17.70422085822753</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -859,10 +866,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>-8.634246567182217</v>
+        <v>-10.32818271504884</v>
       </c>
       <c r="D10" t="n">
-        <v>-17.98590593535273</v>
+        <v>9.479599790308342</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -879,10 +886,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.9179955011884928</v>
+        <v>-10.55346123029825</v>
       </c>
       <c r="D11" t="n">
-        <v>8.221877705926815</v>
+        <v>8.020785170490411</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -899,10 +906,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.5221679191191271</v>
+        <v>16.04255249472128</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.52744229607183</v>
+        <v>2.290772923465952</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -919,10 +926,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.869572360546456</v>
+        <v>-7.086487760559926</v>
       </c>
       <c r="D13" t="n">
-        <v>14.00225299729911</v>
+        <v>4.035577394917353</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -939,10 +946,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>19.5037380693124</v>
+        <v>16.74046363332193</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.969874668134551</v>
+        <v>-4.305734760551586</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -959,10 +966,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6.650452359280791</v>
+        <v>-5.938798193498763</v>
       </c>
       <c r="D15" t="n">
-        <v>-18.94785095803532</v>
+        <v>9.907537890770882</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -979,10 +986,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>8.819047718307928</v>
+        <v>12.83422828743795</v>
       </c>
       <c r="D16" t="n">
-        <v>3.819299600338695</v>
+        <v>-9.557348754083264</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -999,10 +1006,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>-16.40687471406214</v>
+        <v>11.8019786398993</v>
       </c>
       <c r="D17" t="n">
-        <v>14.95889613445267</v>
+        <v>-6.702548910423928</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -1019,10 +1026,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>5.719586926414387</v>
+        <v>-15.27406783503279</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.628332975108989</v>
+        <v>2.761848113869746</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -1039,10 +1046,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>-10.01269538054338</v>
+        <v>-4.834730488292834</v>
       </c>
       <c r="D19" t="n">
-        <v>7.837745334597315</v>
+        <v>-23.01933872568203</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -1059,10 +1066,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>19.25515532885564</v>
+        <v>9.996879782450131</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.743097604737869</v>
+        <v>-21.96991246467039</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -1079,10 +1086,10 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>10.73057165210123</v>
+        <v>-11.06057874938554</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8031920278743598</v>
+        <v>1.579680160257112</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -1099,10 +1106,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>7.977089495017879</v>
+        <v>-12.89647450282712</v>
       </c>
       <c r="D22" t="n">
-        <v>10.37880305918925</v>
+        <v>-11.43055333189162</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -1119,10 +1126,10 @@
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>7.493755896275346</v>
+        <v>8.044677671473679</v>
       </c>
       <c r="D23" t="n">
-        <v>16.1361602703834</v>
+        <v>22.96478865975635</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -1139,10 +1146,10 @@
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>17.83827437853432</v>
+        <v>16.80346766296749</v>
       </c>
       <c r="D24" t="n">
-        <v>9.969068960778429</v>
+        <v>16.47057153257236</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -1159,10 +1166,10 @@
         <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>-4.093819670199885</v>
+        <v>19.61369183800984</v>
       </c>
       <c r="D25" t="n">
-        <v>10.78124209171258</v>
+        <v>6.506126959813145</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -1179,10 +1186,10 @@
         <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>-7.304112753397412</v>
+        <v>-9.330867602360641</v>
       </c>
       <c r="D26" t="n">
-        <v>11.66910645575301</v>
+        <v>0.3059773796144469</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -1199,10 +1206,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>-11.00735135144004</v>
+        <v>12.63613614180791</v>
       </c>
       <c r="D27" t="n">
-        <v>5.320278319944421</v>
+        <v>1.069530031619408</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -1219,10 +1226,10 @@
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>-13.8251560104538</v>
+        <v>15.10306711944041</v>
       </c>
       <c r="D28" t="n">
-        <v>-15.2843200875859</v>
+        <v>14.35031542128742</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -1239,10 +1246,10 @@
         <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>-4.682845954171761</v>
+        <v>10.2020036471682</v>
       </c>
       <c r="D29" t="n">
-        <v>4.028985546370478</v>
+        <v>22.65732588813449</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -1259,10 +1266,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5452164101629293</v>
+        <v>20.65587744102102</v>
       </c>
       <c r="D30" t="n">
-        <v>-12.58571342026514</v>
+        <v>7.776491020567832</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -1279,10 +1286,10 @@
         <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>-15.33826650666168</v>
+        <v>-15.09357680517539</v>
       </c>
       <c r="D31" t="n">
-        <v>-12.23453636512133</v>
+        <v>5.941146935381724</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -1299,10 +1306,10 @@
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>19.06163247574779</v>
+        <v>6.575471258442192</v>
       </c>
       <c r="D32" t="n">
-        <v>-10.68416880801502</v>
+        <v>-15.20326139720933</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -1319,10 +1326,10 @@
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>-4.997370074282479</v>
+        <v>-10.43474926122941</v>
       </c>
       <c r="D33" t="n">
-        <v>14.21196775710676</v>
+        <v>-14.53206531089718</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -1339,10 +1346,10 @@
         <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>-12.22419302303832</v>
+        <v>-9.977079767545661</v>
       </c>
       <c r="D34" t="n">
-        <v>8.643427462128045</v>
+        <v>15.83171377684923</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -1359,10 +1366,10 @@
         <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>10.20128543515487</v>
+        <v>-2.389809673317487</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.178068413328887</v>
+        <v>-3.267060672647943</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
@@ -1379,10 +1386,10 @@
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>-12.08492454333855</v>
+        <v>7.607618445038653</v>
       </c>
       <c r="D36" t="n">
-        <v>9.288158609218371</v>
+        <v>8.655796549829175</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -1399,10 +1406,10 @@
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>3.610291046092165</v>
+        <v>7.278668947180876</v>
       </c>
       <c r="D37" t="n">
-        <v>3.517944504693787</v>
+        <v>1.444568317684272</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -1419,10 +1426,10 @@
         <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>17.36321476740133</v>
+        <v>-6.648384777550562</v>
       </c>
       <c r="D38" t="n">
-        <v>1.60154682345275</v>
+        <v>21.0469132918373</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -1439,10 +1446,10 @@
         <v>37</v>
       </c>
       <c r="C39" t="n">
-        <v>11.3615903860358</v>
+        <v>14.58343516074005</v>
       </c>
       <c r="D39" t="n">
-        <v>-4.484962894586644</v>
+        <v>11.83840025902228</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -1459,10 +1466,10 @@
         <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>-10.64164059114805</v>
+        <v>-17.65236422260124</v>
       </c>
       <c r="D40" t="n">
-        <v>2.534890400583947</v>
+        <v>5.383529273143424</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -1479,16 +1486,16 @@
         <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.802457073701419</v>
+        <v>-0.3682807821820049</v>
       </c>
       <c r="D41" t="n">
-        <v>4.860002342843856</v>
+        <v>-7.086995656586722</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
       </c>
       <c r="F41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1499,10 +1506,10 @@
         <v>40</v>
       </c>
       <c r="C42" t="n">
-        <v>18.04667585097297</v>
+        <v>15.64717327439749</v>
       </c>
       <c r="D42" t="n">
-        <v>4.371243625434175</v>
+        <v>18.91975688719603</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -1519,10 +1526,10 @@
         <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>-16.97539734578124</v>
+        <v>9.633799311327463</v>
       </c>
       <c r="D43" t="n">
-        <v>-6.812209999606864</v>
+        <v>-6.313661235264873</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -1539,10 +1546,10 @@
         <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>12.79733684379762</v>
+        <v>-15.5671355970745</v>
       </c>
       <c r="D44" t="n">
-        <v>-8.036268786232</v>
+        <v>-15.59915644128273</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -1559,10 +1566,10 @@
         <v>43</v>
       </c>
       <c r="C45" t="n">
-        <v>-6.568787079381316</v>
+        <v>3.214026404672495</v>
       </c>
       <c r="D45" t="n">
-        <v>-17.02641424444721</v>
+        <v>-19.64144785367996</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -1579,10 +1586,10 @@
         <v>44</v>
       </c>
       <c r="C46" t="n">
-        <v>-3.35343885374067</v>
+        <v>6.119767364281372</v>
       </c>
       <c r="D46" t="n">
-        <v>12.95144102572876</v>
+        <v>-13.23721378873438</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -1599,10 +1606,10 @@
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>-10.88627057180144</v>
+        <v>-19.47431945987062</v>
       </c>
       <c r="D47" t="n">
-        <v>0.836914015966812</v>
+        <v>-0.2446600213936421</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -1619,10 +1626,10 @@
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>14.49472235712129</v>
+        <v>-7.754575815394241</v>
       </c>
       <c r="D48" t="n">
-        <v>4.700955489921441</v>
+        <v>22.25927769887195</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -1639,10 +1646,10 @@
         <v>47</v>
       </c>
       <c r="C49" t="n">
-        <v>-12.76776223361325</v>
+        <v>-5.020509047591837</v>
       </c>
       <c r="D49" t="n">
-        <v>9.656624119359236</v>
+        <v>19.40298476679041</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -1659,10 +1666,10 @@
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>-18.27912209909559</v>
+        <v>-6.349702508174545</v>
       </c>
       <c r="D50" t="n">
-        <v>-5.944458757879715</v>
+        <v>-10.93141576468926</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -1679,10 +1686,10 @@
         <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>5.293972429829942</v>
+        <v>11.55208325397895</v>
       </c>
       <c r="D51" t="n">
-        <v>6.365898892891295</v>
+        <v>-2.594142965282529</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -1699,10 +1706,10 @@
         <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>12.22880817625474</v>
+        <v>8.905195128274912</v>
       </c>
       <c r="D52" t="n">
-        <v>-13.67210910750039</v>
+        <v>0.6328811691435305</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -1719,10 +1726,10 @@
         <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1188645956767829</v>
+        <v>12.32981511623489</v>
       </c>
       <c r="D53" t="n">
-        <v>13.3061506418337</v>
+        <v>-5.976887175569317</v>
       </c>
       <c r="E53" t="s">
         <v>17</v>
@@ -1739,15 +1746,55 @@
         <v>52</v>
       </c>
       <c r="C54" t="n">
-        <v>6.471070127194388</v>
+        <v>-8.022617576777357</v>
       </c>
       <c r="D54" t="n">
-        <v>13.6042750421316</v>
+        <v>-0.9540166085869116</v>
       </c>
       <c r="E54" t="s">
         <v>17</v>
       </c>
       <c r="F54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1.271972223678517</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4.762936393809142</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" t="n">
+        <v>5.901819438052478</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-14.97917087907612</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1762,925 +1809,623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="B2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12.07768264651286</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="C2" t="n">
+        <v>23.6679788130077</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>15.03290066092008</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.638463146816595</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="n">
+      <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>19.50707810120585</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="C4" t="n">
+        <v>11.36908837759391</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="n">
+      <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10.23734299679114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" t="n">
+        <v>23.87432497126383</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="n">
+      <c r="B6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11.17708987639076</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" t="n">
+        <v>18.33645025779595</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="n">
+      <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17.48497064794596</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="C7" t="n">
+        <v>18.28885081839581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="n">
+      <c r="B8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.49864117001303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="C8" t="n">
+        <v>21.27033667140947</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="n">
+      <c r="B9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>11.29734640870898</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="C9" t="n">
+        <v>23.1140571947468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1" t="n">
+      <c r="B10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20.81144277573021</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="C10" t="n">
+        <v>14.97282186755557</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="n">
+      <c r="B11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7.362065924250714</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="C11" t="n">
+        <v>13.82482571323672</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1" t="n">
+      <c r="B12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="n">
-        <v>19.72869517164893</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="C12" t="n">
+        <v>17.9863059862221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1" t="n">
+      <c r="B13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E13" t="n">
-        <v>12.89690699718333</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="C13" t="n">
+        <v>8.425747810866286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="1" t="n">
+      <c r="B14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>21.61305145446846</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="C14" t="n">
+        <v>17.07676913234558</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1" t="n">
+      <c r="B15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18.44837706303902</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="C15" t="n">
+        <v>11.80558237977359</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="1" t="n">
+      <c r="B16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="E16" t="n">
-        <v>9.053189011497579</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="C16" t="n">
+        <v>16.47772549903024</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="1" t="n">
+      <c r="B17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" t="n">
-        <v>22.69802128737657</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="C17" t="n">
+        <v>13.54125036596258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1" t="n">
+      <c r="B18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>8.7475153982141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="C18" t="n">
+        <v>15.65036225985333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13.35440912475893</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="B19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23.88169107131525</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="1" t="n">
+      <c r="B20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="E20" t="n">
-        <v>21.23450251709688</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="C20" t="n">
+        <v>25.35433114066483</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="1" t="n">
+      <c r="B21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E21" t="n">
-        <v>10.45077554890572</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="C21" t="n">
+        <v>10.93484895637239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="1" t="n">
+      <c r="B22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" t="n">
-        <v>13.93918512099685</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="C22" t="n">
+        <v>17.68689301346062</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="1" t="n">
+      <c r="B23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="E23" t="n">
-        <v>18.36928911764458</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="C23" t="n">
+        <v>23.65220906664505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="1" t="n">
+      <c r="B24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="E24" t="n">
-        <v>19.51263711882356</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="C24" t="n">
+        <v>23.61576106330585</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="1" t="n">
+      <c r="B25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="D25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E25" t="n">
-        <v>10.93571257171925</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="C25" t="n">
+        <v>20.36203838638883</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="1" t="n">
+      <c r="B26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13.00190760253289</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="C26" t="n">
+        <v>8.935378271498534</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="1" t="n">
+      <c r="B27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E27" t="n">
-        <v>11.16160479240602</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="C27" t="n">
+        <v>13.32528783730165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="1" t="n">
+      <c r="B28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E28" t="n">
-        <v>20.72254636758528</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="C28" t="n">
+        <v>21.2679587631301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="1" t="n">
+      <c r="B29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="D29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" t="n">
-        <v>6.8626982209984</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="C29" t="n">
+        <v>23.58389669454377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="1" t="n">
+      <c r="B30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="D30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E30" t="n">
-        <v>11.93240846913605</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="C30" t="n">
+        <v>21.72455769857014</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="1" t="n">
+      <c r="B31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" t="n">
-        <v>21.79081305902023</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="C31" t="n">
+        <v>16.89219423778091</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="1" t="n">
+      <c r="B32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="E32" t="n">
-        <v>22.47753622783562</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="C32" t="n">
+        <v>17.53313906237907</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="1" t="n">
+      <c r="B33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="D33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="E33" t="n">
-        <v>15.9923296266239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="C33" t="n">
+        <v>19.08400082694883</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="1" t="n">
+      <c r="B34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="D34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="E34" t="n">
-        <v>16.06680638110965</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="C34" t="n">
+        <v>20.02131848331578</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="1" t="n">
+      <c r="B35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="D35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="E35" t="n">
-        <v>9.620911386682685</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="C35" t="n">
+        <v>3.520048015196053</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="1" t="n">
+      <c r="B36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="D36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="E36" t="n">
-        <v>16.34718518213844</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="C36" t="n">
+        <v>9.959798475767085</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1" t="n">
+      <c r="B37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="D37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="E37" t="n">
-        <v>5.953027129629294</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="C37" t="n">
+        <v>9.183288422845569</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="1" t="n">
+      <c r="B38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="D38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="E38" t="n">
-        <v>15.67726701992998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="C38" t="n">
+        <v>22.07463887882934</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="1" t="n">
+      <c r="B39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="D39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="E39" t="n">
-        <v>11.8076696373273</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="C39" t="n">
+        <v>20.14013833317198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="1" t="n">
+      <c r="B40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="D40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="E40" t="n">
-        <v>10.74450567862613</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="C40" t="n">
+        <v>19.93800632331047</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="1" t="n">
+      <c r="B41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="D41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="E41" t="n">
-        <v>6.42900344854303</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="C41" t="n">
+        <v>4.20071873308718</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="1" t="n">
+      <c r="B42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="D42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="E42" t="n">
-        <v>17.79965879028025</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="C42" t="n">
+        <v>25.58656822332529</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="1" t="n">
+      <c r="B43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="D43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16.92592179524047</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="C43" t="n">
+        <v>12.18767999295959</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="1" t="n">
+      <c r="B44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="D44" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="E44" t="n">
-        <v>14.96830751401125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="C44" t="n">
+        <v>21.34049442103249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="1" t="n">
+      <c r="B45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="D45" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="E45" t="n">
-        <v>19.17574278501695</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="C45" t="n">
+        <v>19.38330363578894</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="1" t="n">
+      <c r="B46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="D46" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="E46" t="n">
-        <v>12.98759110265058</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="C46" t="n">
+        <v>14.0078285523334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" s="1" t="n">
+      <c r="B47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="D47" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="E47" t="n">
-        <v>11.17277714941099</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="C47" t="n">
+        <v>20.27629933962165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" s="1" t="n">
+      <c r="B48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="D48" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="E48" t="n">
-        <v>16.40066142884426</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="C48" t="n">
+        <v>23.31749142818731</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="1" t="n">
+      <c r="B49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="D49" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="E49" t="n">
-        <v>17.07083147099415</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="C49" t="n">
+        <v>20.93111724015277</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="1" t="n">
+      <c r="B50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="D50" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="E50" t="n">
-        <v>18.60959621750342</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="C50" t="n">
+        <v>12.96369530722316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="1" t="n">
+      <c r="B51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="D51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="E51" t="n">
-        <v>9.05861654609622</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="C51" t="n">
+        <v>11.43399179771512</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="1" t="n">
+      <c r="B52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="D52" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="E52" t="n">
-        <v>18.68397907897687</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="C52" t="n">
+        <v>10.27283668761884</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="1" t="n">
+      <c r="B53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="D53" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="E53" t="n">
-        <v>14.726582869176</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="C53" t="n">
+        <v>14.56697603070205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" s="1" t="n">
+      <c r="B54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="D54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="E54" t="n">
-        <v>16.54212208475527</v>
+      <c r="C54" t="n">
+        <v>7.498060208961257</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6.8964270541306</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" t="n">
+        <v>17.10117035284206</v>
       </c>
     </row>
   </sheetData>
@@ -2699,13 +2444,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/history_matching/example/iter2/Cuts/RadiusShouldBe15/history_matching_config.xlsx
+++ b/history_matching/example/iter2/Cuts/RadiusShouldBe15/history_matching_config.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>Parameter</t>
   </si>
@@ -68,172 +68,166 @@
     <t>Train</t>
   </si>
   <si>
-    <t>Data_20180119_074635.000000</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000001</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000002</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000003</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000004</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000005</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000006</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000007</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000008</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000009</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000010</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000011</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000012</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000013</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000014</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000015</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000016</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000017</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000018</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000019</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000020</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000021</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000022</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000023</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000024</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000025</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000026</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000027</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000028</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000029</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000030</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000031</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000032</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000033</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000034</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000035</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000036</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000037</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000038</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000039</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000040</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000041</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000042</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000043</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000044</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000045</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000046</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000047</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000048</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000049</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000050</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000051</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000052</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000053</t>
-  </si>
-  <si>
-    <t>Data_20180119_074635.000054</t>
+    <t>Data_20180120_214437.000000</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000001</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000002</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000003</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000004</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000005</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000006</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000007</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000008</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000009</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000010</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000011</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000012</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000013</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000014</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000015</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000016</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000017</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000018</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000019</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000020</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000021</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000022</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000023</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000024</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000025</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000026</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000027</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000028</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000029</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000030</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000031</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000032</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000033</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000034</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000035</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000036</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000037</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000038</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000039</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000040</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000041</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000042</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000043</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000044</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000045</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000046</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000047</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000048</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000049</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000050</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000051</t>
+  </si>
+  <si>
+    <t>Data_20180120_214437.000052</t>
   </si>
   <si>
     <t>Sim_Id</t>
@@ -675,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -706,10 +700,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-12.14684535151868</v>
+        <v>0.8497631804685568</v>
       </c>
       <c r="D2" t="n">
-        <v>-19.8468228003866</v>
+        <v>23.73824328809854</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -726,10 +720,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>4.904898148493372</v>
+        <v>-12.02577157496209</v>
       </c>
       <c r="D3" t="n">
-        <v>1.967001998453881</v>
+        <v>7.329832517009407</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -746,10 +740,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>10.17802948191527</v>
+        <v>-26.85344877644219</v>
       </c>
       <c r="D4" t="n">
-        <v>-6.083306211143764</v>
+        <v>-8.024554673998978</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -766,10 +760,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>-6.753743942882013</v>
+        <v>-41.51523604339693</v>
       </c>
       <c r="D5" t="n">
-        <v>-22.76013445207743</v>
+        <v>1.695286475258826</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -786,10 +780,10 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.189547005439286</v>
+        <v>-0.9279999012154859</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.99828556386437</v>
+        <v>11.59125859863062</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -806,10 +800,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.256059070692373</v>
+        <v>14.40102347153904</v>
       </c>
       <c r="D7" t="n">
-        <v>-18.05910606199234</v>
+        <v>-13.78234962365453</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -826,10 +820,10 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.54903056732685</v>
+        <v>12.05979556706487</v>
       </c>
       <c r="D8" t="n">
-        <v>-17.39727569829309</v>
+        <v>-2.419547785385788</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -846,10 +840,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>13.89487980954055</v>
+        <v>8.08929013779364</v>
       </c>
       <c r="D9" t="n">
-        <v>-17.70422085822753</v>
+        <v>-5.092869639841126</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -866,10 +860,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>-10.32818271504884</v>
+        <v>-35.53491263899764</v>
       </c>
       <c r="D10" t="n">
-        <v>9.479599790308342</v>
+        <v>5.957431075549025</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -886,10 +880,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>-10.55346123029825</v>
+        <v>-29.45294621644173</v>
       </c>
       <c r="D11" t="n">
-        <v>8.020785170490411</v>
+        <v>4.946896342389834</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -906,10 +900,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>16.04255249472128</v>
+        <v>18.48648211040055</v>
       </c>
       <c r="D12" t="n">
-        <v>2.290772923465952</v>
+        <v>15.29491702411593</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -926,10 +920,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-7.086487760559926</v>
+        <v>-11.92542118768872</v>
       </c>
       <c r="D13" t="n">
-        <v>4.035577394917353</v>
+        <v>10.21862605482636</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -946,10 +940,10 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>16.74046363332193</v>
+        <v>0.5013583610587204</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.305734760551586</v>
+        <v>15.70475902611797</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -966,10 +960,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>-5.938798193498763</v>
+        <v>19.99204617787428</v>
       </c>
       <c r="D15" t="n">
-        <v>9.907537890770882</v>
+        <v>-7.046686921402028</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -986,10 +980,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>12.83422828743795</v>
+        <v>-17.01004198513147</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.557348754083264</v>
+        <v>-8.052908250234296</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -1006,10 +1000,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>11.8019786398993</v>
+        <v>10.41102292794746</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.702548910423928</v>
+        <v>16.89752377037026</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -1026,10 +1020,10 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-15.27406783503279</v>
+        <v>2.631698847571798</v>
       </c>
       <c r="D18" t="n">
-        <v>2.761848113869746</v>
+        <v>9.069564194801076</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -1046,10 +1040,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>-4.834730488292834</v>
+        <v>-16.4109885128295</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.01933872568203</v>
+        <v>8.665899695735076</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -1066,10 +1060,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>9.996879782450131</v>
+        <v>-16.56110675700298</v>
       </c>
       <c r="D20" t="n">
-        <v>-21.96991246467039</v>
+        <v>2.197006845589229</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -1086,10 +1080,10 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>-11.06057874938554</v>
+        <v>-13.57908488015537</v>
       </c>
       <c r="D21" t="n">
-        <v>1.579680160257112</v>
+        <v>-4.234143726252498</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -1106,10 +1100,10 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>-12.89647450282712</v>
+        <v>15.03625410793309</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.43055333189162</v>
+        <v>-10.47285004820868</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -1126,10 +1120,10 @@
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>8.044677671473679</v>
+        <v>-10.08081167242276</v>
       </c>
       <c r="D23" t="n">
-        <v>22.96478865975635</v>
+        <v>14.8457780369409</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -1146,10 +1140,10 @@
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>16.80346766296749</v>
+        <v>-14.43425957086176</v>
       </c>
       <c r="D24" t="n">
-        <v>16.47057153257236</v>
+        <v>3.052652185257472</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -1166,10 +1160,10 @@
         <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>19.61369183800984</v>
+        <v>-41.90001253276814</v>
       </c>
       <c r="D25" t="n">
-        <v>6.506126959813145</v>
+        <v>4.380172249458369</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -1186,10 +1180,10 @@
         <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>-9.330867602360641</v>
+        <v>-15.23491735759201</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3059773796144469</v>
+        <v>3.800184448019621</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -1206,10 +1200,10 @@
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>12.63613614180791</v>
+        <v>-39.36137950218873</v>
       </c>
       <c r="D27" t="n">
-        <v>1.069530031619408</v>
+        <v>6.961533245122182</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -1226,10 +1220,10 @@
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>15.10306711944041</v>
+        <v>-0.03259009239693</v>
       </c>
       <c r="D28" t="n">
-        <v>14.35031542128742</v>
+        <v>-10.10950871589915</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -1246,10 +1240,10 @@
         <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>10.2020036471682</v>
+        <v>-31.92573329309284</v>
       </c>
       <c r="D29" t="n">
-        <v>22.65732588813449</v>
+        <v>-12.75102662144095</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -1266,10 +1260,10 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>20.65587744102102</v>
+        <v>14.08712021271873</v>
       </c>
       <c r="D30" t="n">
-        <v>7.776491020567832</v>
+        <v>0.5474653959434335</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -1286,10 +1280,10 @@
         <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>-15.09357680517539</v>
+        <v>-19.59977597091169</v>
       </c>
       <c r="D31" t="n">
-        <v>5.941146935381724</v>
+        <v>7.802351578417416</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -1306,10 +1300,10 @@
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>6.575471258442192</v>
+        <v>9.051791998093172</v>
       </c>
       <c r="D32" t="n">
-        <v>-15.20326139720933</v>
+        <v>-16.17092341658406</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -1326,10 +1320,10 @@
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>-10.43474926122941</v>
+        <v>-24.24404167657215</v>
       </c>
       <c r="D33" t="n">
-        <v>-14.53206531089718</v>
+        <v>-6.301145860923412</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -1346,10 +1340,10 @@
         <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>-9.977079767545661</v>
+        <v>2.862106452276294</v>
       </c>
       <c r="D34" t="n">
-        <v>15.83171377684923</v>
+        <v>-13.81109939610121</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -1366,10 +1360,10 @@
         <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>-2.389809673317487</v>
+        <v>-38.73014971641683</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.267060672647943</v>
+        <v>-5.842758186235869</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
@@ -1386,10 +1380,10 @@
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>7.607618445038653</v>
+        <v>-23.0117549770495</v>
       </c>
       <c r="D36" t="n">
-        <v>8.655796549829175</v>
+        <v>-14.86805480118175</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -1406,10 +1400,10 @@
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>7.278668947180876</v>
+        <v>-7.586088859036651</v>
       </c>
       <c r="D37" t="n">
-        <v>1.444568317684272</v>
+        <v>19.73636498681199</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -1426,10 +1420,10 @@
         <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.648384777550562</v>
+        <v>8.73789248003942</v>
       </c>
       <c r="D38" t="n">
-        <v>21.0469132918373</v>
+        <v>8.200762284205453</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -1446,10 +1440,10 @@
         <v>37</v>
       </c>
       <c r="C39" t="n">
-        <v>14.58343516074005</v>
+        <v>-40.23807994927729</v>
       </c>
       <c r="D39" t="n">
-        <v>11.83840025902228</v>
+        <v>3.977584805922135</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -1466,10 +1460,10 @@
         <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>-17.65236422260124</v>
+        <v>6.735783985791046</v>
       </c>
       <c r="D40" t="n">
-        <v>5.383529273143424</v>
+        <v>-6.521797213862925</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -1486,16 +1480,16 @@
         <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3682807821820049</v>
+        <v>-32.11547826583482</v>
       </c>
       <c r="D41" t="n">
-        <v>-7.086995656586722</v>
+        <v>-7.654971405325099</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
       </c>
       <c r="F41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1506,10 +1500,10 @@
         <v>40</v>
       </c>
       <c r="C42" t="n">
-        <v>15.64717327439749</v>
+        <v>-17.2210854147443</v>
       </c>
       <c r="D42" t="n">
-        <v>18.91975688719603</v>
+        <v>14.37122469349954</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -1526,10 +1520,10 @@
         <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>9.633799311327463</v>
+        <v>-35.12251974097423</v>
       </c>
       <c r="D43" t="n">
-        <v>-6.313661235264873</v>
+        <v>-1.513590034678785</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -1546,10 +1540,10 @@
         <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>-15.5671355970745</v>
+        <v>-16.21642663769896</v>
       </c>
       <c r="D44" t="n">
-        <v>-15.59915644128273</v>
+        <v>8.592593585022641</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -1566,10 +1560,10 @@
         <v>43</v>
       </c>
       <c r="C45" t="n">
-        <v>3.214026404672495</v>
+        <v>0.7704114866391123</v>
       </c>
       <c r="D45" t="n">
-        <v>-19.64144785367996</v>
+        <v>21.65364319293591</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -1586,10 +1580,10 @@
         <v>44</v>
       </c>
       <c r="C46" t="n">
-        <v>6.119767364281372</v>
+        <v>-12.41431378212511</v>
       </c>
       <c r="D46" t="n">
-        <v>-13.23721378873438</v>
+        <v>13.65131719693666</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -1606,10 +1600,10 @@
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>-19.47431945987062</v>
+        <v>-32.95688512640088</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2446600213936421</v>
+        <v>-2.510929373411969</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -1626,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>-7.754575815394241</v>
+        <v>-28.92875655404802</v>
       </c>
       <c r="D48" t="n">
-        <v>22.25927769887195</v>
+        <v>-2.639948799684234</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -1646,10 +1640,10 @@
         <v>47</v>
       </c>
       <c r="C49" t="n">
-        <v>-5.020509047591837</v>
+        <v>-21.22137915573253</v>
       </c>
       <c r="D49" t="n">
-        <v>19.40298476679041</v>
+        <v>6.490156678409704</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -1666,10 +1660,10 @@
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>-6.349702508174545</v>
+        <v>-25.43299411658989</v>
       </c>
       <c r="D50" t="n">
-        <v>-10.93141576468926</v>
+        <v>-14.98760651516247</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -1686,10 +1680,10 @@
         <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>11.55208325397895</v>
+        <v>-6.904847289375829</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.594142965282529</v>
+        <v>-18.4307280362564</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -1706,10 +1700,10 @@
         <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>8.905195128274912</v>
+        <v>-27.82371049578684</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6328811691435305</v>
+        <v>4.827542519883039</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -1726,10 +1720,10 @@
         <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>12.32981511623489</v>
+        <v>11.39004839295535</v>
       </c>
       <c r="D53" t="n">
-        <v>-5.976887175569317</v>
+        <v>-17.05978737646872</v>
       </c>
       <c r="E53" t="s">
         <v>17</v>
@@ -1746,55 +1740,15 @@
         <v>52</v>
       </c>
       <c r="C54" t="n">
-        <v>-8.022617576777357</v>
+        <v>-1.471629036094555</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9540166085869116</v>
+        <v>15.13391593356201</v>
       </c>
       <c r="E54" t="s">
         <v>17</v>
       </c>
       <c r="F54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" t="n">
-        <v>53</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1.271972223678517</v>
-      </c>
-      <c r="D55" t="n">
-        <v>4.762936393809142</v>
-      </c>
-      <c r="E55" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" t="n">
-        <v>54</v>
-      </c>
-      <c r="C56" t="n">
-        <v>5.901819438052478</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-14.97917087907612</v>
-      </c>
-      <c r="E56" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1809,7 +1763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1817,10 +1771,10 @@
         <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1831,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>23.6679788130077</v>
+        <v>24.39657166015621</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1842,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>4.638463146816595</v>
+        <v>13.80479329737066</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1853,7 +1807,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>11.36908837759391</v>
+        <v>29.06326999105486</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1864,7 +1818,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>23.87432497126383</v>
+        <v>41.37719807629199</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1875,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>18.33645025779595</v>
+        <v>11.82669292832045</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1886,7 +1840,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>18.28885081839581</v>
+        <v>21.20510405537468</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1897,7 +1851,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>21.27033667140947</v>
+        <v>13.60611410555557</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1908,7 +1862,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>23.1140571947468</v>
+        <v>8.314140081022504</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1919,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>14.97282186755557</v>
+        <v>37.41704469074293</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1930,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>13.82482571323672</v>
+        <v>30.61111626339154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1941,7 +1895,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>17.9863059862221</v>
+        <v>24.0180734590077</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1952,7 +1906,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>8.425747810866286</v>
+        <v>15.35250593084126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1963,7 +1917,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>17.07676913234558</v>
+        <v>15.1563257919741</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1974,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>11.80558237977359</v>
+        <v>21.87083661879726</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1985,7 +1939,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>16.47772549903024</v>
+        <v>18.31428826135992</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1996,7 +1950,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>13.54125036596258</v>
+        <v>18.27964309771316</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2007,7 +1961,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>15.65036225985333</v>
+        <v>8.956569567739871</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2018,7 +1972,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>23.88169107131525</v>
+        <v>17.76907477084569</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2029,7 +1983,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>25.35433114066483</v>
+        <v>15.44282323516243</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2040,7 +1994,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>10.93484895637239</v>
+        <v>14.12954167972452</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2051,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>17.68689301346062</v>
+        <v>17.05142185515759</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2062,7 +2016,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>23.65220906664505</v>
+        <v>17.58896809499064</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2073,7 +2027,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>23.61576106330585</v>
+        <v>15.54489676727618</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2084,7 +2038,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>20.36203838638883</v>
+        <v>42.48642379401265</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2095,7 +2049,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>8.935378271498534</v>
+        <v>15.91015344265877</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2106,7 +2060,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>13.32528783730165</v>
+        <v>39.75574010138832</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2117,7 +2071,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>21.2679587631301</v>
+        <v>11.20376454891801</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2128,7 +2082,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>23.58389669454377</v>
+        <v>34.05021306630596</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2139,7 +2093,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>21.72455769857014</v>
+        <v>14.88883877769784</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2150,7 +2104,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>16.89219423778091</v>
+        <v>21.21903935697876</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2161,7 +2115,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>17.53313906237907</v>
+        <v>18.07399724949116</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2172,7 +2126,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>19.08400082694883</v>
+        <v>26.06599532052696</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2183,7 +2137,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>20.02131848331578</v>
+        <v>15.64820377908749</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2194,7 +2148,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>3.520048015196053</v>
+        <v>38.298758685184</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2205,7 +2159,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>9.959798475767085</v>
+        <v>27.26949600921141</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2216,7 +2170,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>9.183288422845569</v>
+        <v>20.18005974625354</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2227,7 +2181,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>22.07463887882934</v>
+        <v>11.58475745145461</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2238,7 +2192,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="n">
-        <v>20.14013833317198</v>
+        <v>40.1961231578856</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2249,7 +2203,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>19.93800632331047</v>
+        <v>10.44754326885495</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2260,7 +2214,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="n">
-        <v>4.20071873308718</v>
+        <v>32.73994135871285</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2271,7 +2225,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="n">
-        <v>25.58656822332529</v>
+        <v>21.09146970262135</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2282,7 +2236,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>12.18767999295959</v>
+        <v>37.1835025800134</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2293,7 +2247,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>21.34049442103249</v>
+        <v>18.40345657952444</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2304,7 +2258,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="n">
-        <v>19.38330363578894</v>
+        <v>21.85086396069195</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2315,7 +2269,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="n">
-        <v>14.0078285523334</v>
+        <v>18.54654793798706</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2326,7 +2280,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="n">
-        <v>20.27629933962165</v>
+        <v>32.63951692735998</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -2337,7 +2291,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="n">
-        <v>23.31749142818731</v>
+        <v>29.56602724456997</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -2348,7 +2302,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="n">
-        <v>20.93111724015277</v>
+        <v>21.15111311044681</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -2359,7 +2313,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="n">
-        <v>12.96369530722316</v>
+        <v>31.47507357129949</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -2370,7 +2324,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>11.43399179771512</v>
+        <v>20.56889095849385</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -2381,7 +2335,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="n">
-        <v>10.27283668761884</v>
+        <v>30.63957559157354</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2392,7 +2346,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="n">
-        <v>14.56697603070205</v>
+        <v>20.64054628935165</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2403,29 +2357,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="n">
-        <v>7.498060208961257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="C55" t="n">
-        <v>6.8964270541306</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="C56" t="n">
-        <v>17.10117035284206</v>
+        <v>15.33346870870436</v>
       </c>
     </row>
   </sheetData>
@@ -2444,13 +2376,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">
